--- a/data/trans_orig/P2A_senso_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46399</t>
+          <t>46436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46193</t>
+          <t>48269</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54700</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89079</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>985324</t>
+          <t>985287</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1008045</t>
+          <t>1007630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1268920</t>
+          <t>1266844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1291367</t>
+          <t>1290686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2257756</t>
+          <t>2258882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2292135</t>
+          <t>2291231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>20405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,77 +1096,77 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>16738</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10020</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26754</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>28898</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>19235</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>41267</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>1,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16738</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9765</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27713</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>28898</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>41952</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1672149</t>
+          <t>1673008</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1686909</t>
+          <t>1687012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1538</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1570935</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1560919</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1577653</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3175</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3252188</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3239819</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3261851</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>98,74%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1538</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1570935</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1559960</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1577908</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3175</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3252188</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3239134</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3261045</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540241</t>
+          <t>540461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550342</t>
+          <t>550353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465926</t>
+          <t>465303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474480</t>
+          <t>474465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1009752</t>
+          <t>1010514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1022943</t>
+          <t>1023771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>37661</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>66661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>43136</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73473</t>
+          <t>72447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86200</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127504</t>
+          <t>127417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3210284</t>
+          <t>3209882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3238540</t>
+          <t>3238882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3305724</t>
+          <t>3306750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3336464</t>
+          <t>3336061</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6528237</t>
+          <t>6528324</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6569541</t>
+          <t>6567927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33439</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44722</t>
+          <t>43809</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39764</t>
+          <t>39126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68752</t>
+          <t>68918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>941204</t>
+          <t>941875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>961594</t>
+          <t>961837</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1293075</t>
+          <t>1293988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1315641</t>
+          <t>1316109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2243688</t>
+          <t>2243522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2272676</t>
+          <t>2273314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42320</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20131</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44907</t>
+          <t>42570</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>44517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>76500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1921637</t>
+          <t>1920847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1944216</t>
+          <t>1943876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1712896</t>
+          <t>1715233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1737672</t>
+          <t>1738849</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3645438</t>
+          <t>3645260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3677308</t>
+          <t>3677243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27760</t>
+          <t>27735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35395</t>
+          <t>35207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465101</t>
+          <t>462480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479223</t>
+          <t>478328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>430871</t>
+          <t>430896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449596</t>
+          <t>450088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>904418</t>
+          <t>904606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926313</t>
+          <t>925844</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44892</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76601</t>
+          <t>77732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60302</t>
+          <t>60347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98723</t>
+          <t>95422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113309</t>
+          <t>111499</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160037</t>
+          <t>160559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3343181</t>
+          <t>3342050</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3374890</t>
+          <t>3375042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3455507</t>
+          <t>3458808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3493928</t>
+          <t>3493883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6813975</t>
+          <t>6813453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6860703</t>
+          <t>6862513</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>21025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26090</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17480</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41791</t>
+          <t>41829</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>732364</t>
+          <t>733322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748090</t>
+          <t>748412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>968570</t>
+          <t>967985</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>986092</t>
+          <t>985669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1707216</t>
+          <t>1707178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1731527</t>
+          <t>1730381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29574</t>
+          <t>30955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>30239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26680</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54345</t>
+          <t>52969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2046811</t>
+          <t>2045430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2065747</t>
+          <t>2065972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1958519</t>
+          <t>1958061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1976103</t>
+          <t>1975732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4010340</t>
+          <t>4011716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4038005</t>
+          <t>4037567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537874</t>
+          <t>537676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545937</t>
+          <t>545935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542294</t>
+          <t>543335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1084323</t>
+          <t>1083757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1094045</t>
+          <t>1094028</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48898</t>
+          <t>49377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26718</t>
+          <t>26449</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52548</t>
+          <t>51435</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55658</t>
+          <t>56346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92274</t>
+          <t>90847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3328720</t>
+          <t>3328241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3354023</t>
+          <t>3354009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3479552</t>
+          <t>3480665</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3505382</t>
+          <t>3505651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6817444</t>
+          <t>6818871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6854060</t>
+          <t>6853372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>25790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36483</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54965</t>
+          <t>54600</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50970</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75506</t>
+          <t>75476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489112</t>
+          <t>489148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504296</t>
+          <t>504550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>700543</t>
+          <t>700908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>719025</t>
+          <t>720428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1194940</t>
+          <t>1194970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1219476</t>
+          <t>1219806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31837</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65505</t>
+          <t>66594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46251</t>
+          <t>47114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>804430</t>
+          <t>740535</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91723</t>
+          <t>90801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1021676</t>
+          <t>982589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2224822</t>
+          <t>2223733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2258490</t>
+          <t>2258498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1433393</t>
+          <t>1497288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2191572</t>
+          <t>2190709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3506474</t>
+          <t>3545561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4436427</t>
+          <t>4437349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>20037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16045</t>
+          <t>16496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>32498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626986</t>
+          <t>626586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640200</t>
+          <t>640091</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644418</t>
+          <t>643967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654340</t>
+          <t>653971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1275577</t>
+          <t>1274588</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1292000</t>
+          <t>1291455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54201</t>
+          <t>56818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96586</t>
+          <t>96302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,47 +6586,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>307037</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>102313</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>917779</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>2,8%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>307037</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>101559</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>937156</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174249</t>
+          <t>173739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1098750</t>
+          <t>1177030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3355303</t>
+          <t>3355587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3397688</t>
+          <t>3395071</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,49 +6699,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5171</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3346757</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2736015</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3551481</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>91,6%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>74,88%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>97,2%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5171</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3346757</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2716638</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3552235</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,6%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>74,35%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>8450</t>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6006933</t>
+          <t>5928653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6931434</t>
+          <t>6931944</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_senso_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>24032</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46436</t>
+          <t>48026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>23759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48269</t>
+          <t>47225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55604</t>
+          <t>53428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87953</t>
+          <t>84904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>985287</t>
+          <t>983697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1007630</t>
+          <t>1007691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1266844</t>
+          <t>1267888</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1290686</t>
+          <t>1291354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2258882</t>
+          <t>2261931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2291231</t>
+          <t>2293407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26754</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>19752</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41267</t>
+          <t>41887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1673008</t>
+          <t>1671973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1687012</t>
+          <t>1686786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1560919</t>
+          <t>1560620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1577653</t>
+          <t>1577692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3239819</t>
+          <t>3239199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3261851</t>
+          <t>3261334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540461</t>
+          <t>540407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550353</t>
+          <t>550348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465303</t>
+          <t>465418</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474465</t>
+          <t>474461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1010514</t>
+          <t>1010384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1023771</t>
+          <t>1023796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66661</t>
+          <t>65606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43136</t>
+          <t>43055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72447</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>87785</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127417</t>
+          <t>127834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3209882</t>
+          <t>3210937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3238882</t>
+          <t>3238841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3306750</t>
+          <t>3305655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3336061</t>
+          <t>3336142</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6528324</t>
+          <t>6527907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6567927</t>
+          <t>6567956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>35071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21688</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43809</t>
+          <t>43568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68918</t>
+          <t>69968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>941875</t>
+          <t>939572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>961837</t>
+          <t>960387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1293988</t>
+          <t>1294229</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1316109</t>
+          <t>1315797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2243522</t>
+          <t>2242472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2273314</t>
+          <t>2273374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>41386</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>19819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44517</t>
+          <t>45636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76500</t>
+          <t>79786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1920847</t>
+          <t>1922571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1943876</t>
+          <t>1944652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1715233</t>
+          <t>1714839</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1738849</t>
+          <t>1737984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3645260</t>
+          <t>3641974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3677243</t>
+          <t>3676124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27735</t>
+          <t>26277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462480</t>
+          <t>465124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478328</t>
+          <t>479034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>430896</t>
+          <t>432354</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>450088</t>
+          <t>450066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>904606</t>
+          <t>904439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>925844</t>
+          <t>926745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44740</t>
+          <t>44885</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77732</t>
+          <t>75358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60347</t>
+          <t>59141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95422</t>
+          <t>97084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111499</t>
+          <t>111870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160559</t>
+          <t>160873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3342050</t>
+          <t>3344424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3375042</t>
+          <t>3374897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3458808</t>
+          <t>3457146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3493883</t>
+          <t>3495089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6813453</t>
+          <t>6813139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6862513</t>
+          <t>6862142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21025</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>26433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41829</t>
+          <t>42308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>733322</t>
+          <t>732259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748412</t>
+          <t>747929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>967985</t>
+          <t>968227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>985669</t>
+          <t>985623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1707178</t>
+          <t>1706699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1730381</t>
+          <t>1730803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30955</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30239</t>
+          <t>31419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27118</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52969</t>
+          <t>51541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2045430</t>
+          <t>2047613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2065972</t>
+          <t>2066538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1958061</t>
+          <t>1956881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1975732</t>
+          <t>1975862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4011716</t>
+          <t>4013144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4037567</t>
+          <t>4038811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,42 +4680,42 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>5657</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>11633</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,06%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>5657</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>12270</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>537676</t>
+          <t>538046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545935</t>
+          <t>545926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>543335</t>
+          <t>542852</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,42 +4788,42 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1090370</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1084394</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1094096</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>98,94%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1090370</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1083757</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1094028</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23609</t>
+          <t>23651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49377</t>
+          <t>49784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,44 +4988,44 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>37722</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>26176</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>51679</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>37722</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26449</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>51435</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>65</t>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56346</t>
+          <t>55813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90847</t>
+          <t>91716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3328241</t>
+          <t>3327834</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3354009</t>
+          <t>3353967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,47 +5096,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3494378</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3480421</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3505924</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>98,54%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3291</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3494378</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3480665</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3505651</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6818871</t>
+          <t>6818002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6853372</t>
+          <t>6853905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16786</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25790</t>
+          <t>27846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45053</t>
+          <t>50561</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>41030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54600</t>
+          <t>63464</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>61838</t>
+          <t>68680</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50640</t>
+          <t>56995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75476</t>
+          <t>82782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>498152</t>
+          <t>560410</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489148</t>
+          <t>550683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504550</t>
+          <t>567219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>710455</t>
+          <t>771477</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>700908</t>
+          <t>758574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>720428</t>
+          <t>781008</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1208608</t>
+          <t>1331887</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1194970</t>
+          <t>1317785</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1219806</t>
+          <t>1343572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>56416</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>42530</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66594</t>
+          <t>75432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>251331</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47114</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>740535</t>
+          <t>72544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>298756</t>
+          <t>113095</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90801</t>
+          <t>93774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>982589</t>
+          <t>136276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2242902</t>
+          <t>2174150</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2223733</t>
+          <t>2155134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2258498</t>
+          <t>2188036</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1986492</t>
+          <t>2114713</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1497288</t>
+          <t>2098848</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2190709</t>
+          <t>2126323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4229394</t>
+          <t>4288864</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3545561</t>
+          <t>4265683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4437349</t>
+          <t>4308185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20037</t>
+          <t>22548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16496</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>25579</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15631</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>35242</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>634781</t>
+          <t>698985</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626586</t>
+          <t>689039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640091</t>
+          <t>704159</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>649809</t>
+          <t>721900</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643967</t>
+          <t>715615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653971</t>
+          <t>726646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,27 +6406,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1284590</t>
+          <t>1420885</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1274588</t>
+          <t>1411222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291455</t>
+          <t>1429102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76052</t>
+          <t>87137</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>68822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96302</t>
+          <t>109171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>307037</t>
+          <t>120218</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102313</t>
+          <t>101278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>917779</t>
+          <t>140115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>383089</t>
+          <t>207354</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173739</t>
+          <t>183507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1177030</t>
+          <t>235458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3375837</t>
+          <t>3433546</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3355587</t>
+          <t>3411512</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3395071</t>
+          <t>3451861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3346757</t>
+          <t>3608089</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2736015</t>
+          <t>3588192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3551481</t>
+          <t>3627029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6722594</t>
+          <t>7041636</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5928653</t>
+          <t>7013532</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6931944</t>
+          <t>7065483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_senso_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
